--- a/data/raw/inventory/Week 34/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 34/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -1016,7 +1016,7 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F10" t="n">
         <v>1</v>
@@ -1031,10 +1031,10 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="n">
         <v>1</v>
-      </c>
-      <c r="K10" t="n">
-        <v>2</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
@@ -1202,7 +1202,7 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F13" t="n">
         <v>4</v>
@@ -1211,7 +1211,7 @@
         <v>0</v>
       </c>
       <c r="H13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
@@ -1220,7 +1220,7 @@
         <v>0</v>
       </c>
       <c r="K13" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L13" t="n">
         <v>0</v>
@@ -1574,7 +1574,7 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="F19" t="n">
         <v>0</v>
@@ -1583,16 +1583,16 @@
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>5</v>
+        <v>2</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
@@ -1760,7 +1760,7 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F22" t="n">
         <v>1</v>
@@ -1775,10 +1775,10 @@
         <v>0</v>
       </c>
       <c r="J22" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" t="n">
         <v>1</v>
-      </c>
-      <c r="K22" t="n">
-        <v>2</v>
       </c>
       <c r="L22" t="n">
         <v>0</v>
@@ -2132,10 +2132,10 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G28" t="n">
         <v>0</v>
@@ -2150,7 +2150,7 @@
         <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L28" t="n">
         <v>0</v>
@@ -2380,7 +2380,7 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F32" t="n">
         <v>0</v>
@@ -2395,10 +2395,10 @@
         <v>0</v>
       </c>
       <c r="J32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F35" t="n">
         <v>0</v>
@@ -2581,10 +2581,10 @@
         <v>0</v>
       </c>
       <c r="J35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
@@ -2690,7 +2690,7 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F37" t="n">
         <v>0</v>
@@ -2699,7 +2699,7 @@
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I37" t="n">
         <v>0</v>
@@ -2708,7 +2708,7 @@
         <v>1</v>
       </c>
       <c r="K37" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
@@ -3186,7 +3186,7 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F45" t="n">
         <v>12</v>
@@ -3195,16 +3195,16 @@
         <v>0</v>
       </c>
       <c r="H45" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I45" t="n">
         <v>0</v>
       </c>
       <c r="J45" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="L45" t="n">
         <v>0</v>
@@ -3310,16 +3310,16 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F47" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G47" t="n">
         <v>0</v>
       </c>
       <c r="H47" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
@@ -3328,7 +3328,7 @@
         <v>0</v>
       </c>
       <c r="K47" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L47" t="n">
         <v>0</v>
@@ -3868,25 +3868,25 @@
         </is>
       </c>
       <c r="E56" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" t="n">
+        <v>0</v>
+      </c>
+      <c r="H56" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" t="n">
+        <v>0</v>
+      </c>
+      <c r="J56" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" t="n">
         <v>1</v>
-      </c>
-      <c r="F56" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" t="n">
-        <v>0</v>
-      </c>
-      <c r="J56" t="n">
-        <v>1</v>
-      </c>
-      <c r="K56" t="n">
-        <v>2</v>
       </c>
       <c r="L56" t="n">
         <v>1</v>
@@ -4054,7 +4054,7 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="F59" t="n">
         <v>2</v>
@@ -4063,16 +4063,16 @@
         <v>0</v>
       </c>
       <c r="H59" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I59" t="n">
         <v>1</v>
       </c>
       <c r="J59" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K59" t="n">
-        <v>7</v>
+        <v>4</v>
       </c>
       <c r="L59" t="n">
         <v>0</v>
@@ -4736,7 +4736,7 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F70" t="n">
         <v>4</v>
@@ -4745,7 +4745,7 @@
         <v>0</v>
       </c>
       <c r="H70" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
@@ -4754,7 +4754,7 @@
         <v>0</v>
       </c>
       <c r="K70" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L70" t="n">
         <v>0</v>
@@ -4922,10 +4922,10 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F73" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="G73" t="n">
         <v>0</v>
@@ -4940,7 +4940,7 @@
         <v>0</v>
       </c>
       <c r="K73" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="L73" t="n">
         <v>1</v>
@@ -5108,7 +5108,7 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F76" t="n">
         <v>6</v>
@@ -5117,7 +5117,7 @@
         <v>0</v>
       </c>
       <c r="H76" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I76" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="K76" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L76" t="n">
         <v>0</v>
@@ -5170,10 +5170,10 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="F77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G77" t="n">
         <v>0</v>
@@ -5185,10 +5185,10 @@
         <v>0</v>
       </c>
       <c r="J77" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K77" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L77" t="n">
         <v>0</v>
@@ -5232,10 +5232,10 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F78" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G78" t="n">
         <v>0</v>
@@ -5250,7 +5250,7 @@
         <v>3</v>
       </c>
       <c r="K78" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L78" t="n">
         <v>0</v>
@@ -5356,7 +5356,7 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F80" t="n">
         <v>0</v>
@@ -5365,7 +5365,7 @@
         <v>0</v>
       </c>
       <c r="H80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I80" t="n">
         <v>0</v>
@@ -5374,7 +5374,7 @@
         <v>0</v>
       </c>
       <c r="K80" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L80" t="n">
         <v>0</v>
@@ -5604,7 +5604,7 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F84" t="n">
         <v>2</v>
@@ -5613,7 +5613,7 @@
         <v>0</v>
       </c>
       <c r="H84" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I84" t="n">
         <v>0</v>
@@ -5622,7 +5622,7 @@
         <v>0</v>
       </c>
       <c r="K84" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L84" t="n">
         <v>0</v>
@@ -5852,7 +5852,7 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F88" t="n">
         <v>3</v>
@@ -5867,10 +5867,10 @@
         <v>0</v>
       </c>
       <c r="J88" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K88" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L88" t="n">
         <v>0</v>
@@ -5917,19 +5917,19 @@
         <v>5</v>
       </c>
       <c r="F89" t="n">
+        <v>3</v>
+      </c>
+      <c r="G89" t="n">
+        <v>0</v>
+      </c>
+      <c r="H89" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" t="n">
+        <v>0</v>
+      </c>
+      <c r="J89" t="n">
         <v>2</v>
-      </c>
-      <c r="G89" t="n">
-        <v>0</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" t="n">
-        <v>0</v>
-      </c>
-      <c r="J89" t="n">
-        <v>3</v>
       </c>
       <c r="K89" t="n">
         <v>5</v>
@@ -6038,10 +6038,10 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F91" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G91" t="n">
         <v>0</v>
@@ -6056,7 +6056,7 @@
         <v>3</v>
       </c>
       <c r="K91" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L91" t="n">
         <v>0</v>
@@ -6596,7 +6596,7 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F100" t="n">
         <v>2</v>
@@ -6611,10 +6611,10 @@
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K100" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L100" t="n">
         <v>0</v>
@@ -6844,10 +6844,10 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="F104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G104" t="n">
         <v>0</v>
@@ -6862,7 +6862,7 @@
         <v>0</v>
       </c>
       <c r="K104" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L104" t="n">
         <v>0</v>
@@ -7030,7 +7030,7 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F107" t="n">
         <v>2</v>
@@ -7045,10 +7045,10 @@
         <v>0</v>
       </c>
       <c r="J107" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" t="n">
         <v>2</v>
-      </c>
-      <c r="K107" t="n">
-        <v>4</v>
       </c>
       <c r="L107" t="n">
         <v>0</v>
@@ -7340,7 +7340,7 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F112" t="n">
         <v>2</v>
@@ -7349,7 +7349,7 @@
         <v>0</v>
       </c>
       <c r="H112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I112" t="n">
         <v>0</v>
@@ -7358,7 +7358,7 @@
         <v>0</v>
       </c>
       <c r="K112" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L112" t="n">
         <v>0</v>
@@ -7402,10 +7402,10 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="G113" t="n">
         <v>0</v>
@@ -7420,7 +7420,7 @@
         <v>0</v>
       </c>
       <c r="K113" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="L113" t="n">
         <v>0</v>
@@ -7464,7 +7464,7 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F114" t="n">
         <v>1</v>
@@ -7473,16 +7473,16 @@
         <v>0</v>
       </c>
       <c r="H114" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" t="n">
+        <v>0</v>
+      </c>
+      <c r="J114" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" t="n">
         <v>1</v>
-      </c>
-      <c r="I114" t="n">
-        <v>0</v>
-      </c>
-      <c r="J114" t="n">
-        <v>0</v>
-      </c>
-      <c r="K114" t="n">
-        <v>2</v>
       </c>
       <c r="L114" t="n">
         <v>0</v>
@@ -7588,10 +7588,10 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F116" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G116" t="n">
         <v>0</v>
@@ -7606,7 +7606,7 @@
         <v>0</v>
       </c>
       <c r="K116" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L116" t="n">
         <v>0</v>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F118" t="n">
         <v>3</v>
@@ -7721,7 +7721,7 @@
         <v>0</v>
       </c>
       <c r="H118" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="I118" t="n">
         <v>0</v>
@@ -7730,7 +7730,7 @@
         <v>0</v>
       </c>
       <c r="K118" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="L118" t="n">
         <v>0</v>
@@ -7960,7 +7960,7 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F122" t="n">
         <v>7</v>
@@ -7969,7 +7969,7 @@
         <v>0</v>
       </c>
       <c r="H122" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I122" t="n">
         <v>0</v>
@@ -7978,7 +7978,7 @@
         <v>0</v>
       </c>
       <c r="K122" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="L122" t="n">
         <v>1</v>
@@ -8084,7 +8084,7 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F124" t="n">
         <v>5</v>
@@ -8099,10 +8099,10 @@
         <v>0</v>
       </c>
       <c r="J124" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K124" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L124" t="n">
         <v>0</v>
@@ -8149,7 +8149,7 @@
         <v>182</v>
       </c>
       <c r="F125" t="n">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="G125" t="n">
         <v>0</v>
@@ -8161,7 +8161,7 @@
         <v>1</v>
       </c>
       <c r="J125" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K125" t="n">
         <v>187</v>
@@ -8208,7 +8208,7 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="F126" t="n">
         <v>19</v>
@@ -8217,7 +8217,7 @@
         <v>0</v>
       </c>
       <c r="H126" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="I126" t="n">
         <v>0</v>
@@ -8226,7 +8226,7 @@
         <v>0</v>
       </c>
       <c r="K126" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="L126" t="n">
         <v>0</v>
@@ -8332,7 +8332,7 @@
         </is>
       </c>
       <c r="E128" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="F128" t="n">
         <v>9</v>
@@ -8341,7 +8341,7 @@
         <v>0</v>
       </c>
       <c r="H128" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I128" t="n">
         <v>0</v>
@@ -8350,7 +8350,7 @@
         <v>0</v>
       </c>
       <c r="K128" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="L128" t="n">
         <v>0</v>
@@ -8518,10 +8518,10 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G131" t="n">
         <v>0</v>
@@ -8536,7 +8536,7 @@
         <v>0</v>
       </c>
       <c r="K131" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L131" t="n">
         <v>0</v>
@@ -8580,10 +8580,10 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G132" t="n">
         <v>0</v>
@@ -8598,7 +8598,7 @@
         <v>0</v>
       </c>
       <c r="K132" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L132" t="n">
         <v>0</v>
@@ -9386,16 +9386,16 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F145" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="G145" t="n">
         <v>0</v>
       </c>
       <c r="H145" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I145" t="n">
         <v>0</v>
@@ -9404,7 +9404,7 @@
         <v>0</v>
       </c>
       <c r="K145" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L145" t="n">
         <v>0</v>
@@ -10130,7 +10130,7 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F157" t="n">
         <v>1</v>
@@ -10145,10 +10145,10 @@
         <v>0</v>
       </c>
       <c r="J157" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="K157" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="L157" t="n">
         <v>0</v>
@@ -10192,7 +10192,7 @@
         </is>
       </c>
       <c r="E158" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="F158" t="n">
         <v>6</v>
@@ -10201,16 +10201,16 @@
         <v>0</v>
       </c>
       <c r="H158" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="I158" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J158" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K158" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="L158" t="n">
         <v>0</v>
@@ -10319,7 +10319,7 @@
         <v>3</v>
       </c>
       <c r="F160" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G160" t="n">
         <v>0</v>
@@ -10331,7 +10331,7 @@
         <v>0</v>
       </c>
       <c r="J160" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K160" t="n">
         <v>3</v>
@@ -10378,7 +10378,7 @@
         </is>
       </c>
       <c r="E161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F161" t="n">
         <v>0</v>
@@ -10393,10 +10393,10 @@
         <v>0</v>
       </c>
       <c r="J161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K161" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L161" t="n">
         <v>0</v>
@@ -10688,10 +10688,10 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G166" t="n">
         <v>0</v>
@@ -10703,10 +10703,10 @@
         <v>0</v>
       </c>
       <c r="J166" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K166" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L166" t="n">
         <v>0</v>
@@ -10753,7 +10753,7 @@
         <v>7</v>
       </c>
       <c r="F167" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="G167" t="n">
         <v>0</v>
@@ -10765,7 +10765,7 @@
         <v>0</v>
       </c>
       <c r="J167" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K167" t="n">
         <v>7</v>
@@ -11745,7 +11745,7 @@
         <v>9</v>
       </c>
       <c r="F183" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="G183" t="n">
         <v>0</v>
@@ -11757,7 +11757,7 @@
         <v>0</v>
       </c>
       <c r="J183" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="K183" t="n">
         <v>9</v>
@@ -11928,10 +11928,10 @@
         </is>
       </c>
       <c r="E186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="G186" t="n">
         <v>0</v>
@@ -11946,7 +11946,7 @@
         <v>0</v>
       </c>
       <c r="K186" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L186" t="n">
         <v>0</v>
@@ -12176,7 +12176,7 @@
         </is>
       </c>
       <c r="E190" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F190" t="n">
         <v>1</v>
@@ -12191,10 +12191,10 @@
         <v>0</v>
       </c>
       <c r="J190" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K190" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L190" t="n">
         <v>1</v>
@@ -12238,7 +12238,7 @@
         </is>
       </c>
       <c r="E191" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F191" t="n">
         <v>3</v>
@@ -12253,10 +12253,10 @@
         <v>0</v>
       </c>
       <c r="J191" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K191" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L191" t="n">
         <v>0</v>
@@ -12566,10 +12566,10 @@
         <v>0</v>
       </c>
       <c r="K196" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="L196" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M196" t="n">
         <v>0</v>
@@ -12672,16 +12672,16 @@
         </is>
       </c>
       <c r="E198" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="F198" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="G198" t="n">
         <v>0</v>
       </c>
       <c r="H198" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="I198" t="n">
         <v>0</v>
@@ -12690,7 +12690,7 @@
         <v>0</v>
       </c>
       <c r="K198" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="L198" t="n">
         <v>0</v>
@@ -13354,7 +13354,7 @@
         </is>
       </c>
       <c r="E209" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F209" t="n">
         <v>1</v>
@@ -13363,16 +13363,16 @@
         <v>0</v>
       </c>
       <c r="H209" t="n">
+        <v>0</v>
+      </c>
+      <c r="I209" t="n">
+        <v>0</v>
+      </c>
+      <c r="J209" t="n">
+        <v>0</v>
+      </c>
+      <c r="K209" t="n">
         <v>1</v>
-      </c>
-      <c r="I209" t="n">
-        <v>0</v>
-      </c>
-      <c r="J209" t="n">
-        <v>0</v>
-      </c>
-      <c r="K209" t="n">
-        <v>2</v>
       </c>
       <c r="L209" t="n">
         <v>0</v>
@@ -13478,7 +13478,7 @@
         </is>
       </c>
       <c r="E211" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F211" t="n">
         <v>2</v>
@@ -13493,10 +13493,10 @@
         <v>0</v>
       </c>
       <c r="J211" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K211" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L211" t="n">
         <v>0</v>
@@ -13540,7 +13540,7 @@
         </is>
       </c>
       <c r="E212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F212" t="n">
         <v>0</v>
@@ -13555,10 +13555,10 @@
         <v>0</v>
       </c>
       <c r="J212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K212" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L212" t="n">
         <v>0</v>
@@ -13788,7 +13788,7 @@
         </is>
       </c>
       <c r="E216" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F216" t="n">
         <v>2</v>
@@ -13803,10 +13803,10 @@
         <v>0</v>
       </c>
       <c r="J216" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K216" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L216" t="n">
         <v>0</v>
@@ -13989,7 +13989,7 @@
         <v>0</v>
       </c>
       <c r="J219" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K219" t="n">
         <v>10</v>
@@ -13998,7 +13998,7 @@
         <v>0</v>
       </c>
       <c r="M219" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N219" t="inlineStr">
         <is>
@@ -14408,25 +14408,25 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="F226" t="n">
-        <v>718</v>
+        <v>742</v>
       </c>
       <c r="G226" t="n">
         <v>0</v>
       </c>
       <c r="H226" t="n">
-        <v>168</v>
+        <v>144</v>
       </c>
       <c r="I226" t="n">
         <v>0</v>
       </c>
       <c r="J226" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="K226" t="n">
-        <v>892</v>
+        <v>889</v>
       </c>
       <c r="L226" t="n">
         <v>0</v>
@@ -14470,7 +14470,7 @@
         </is>
       </c>
       <c r="E227" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F227" t="n">
         <v>15</v>
@@ -14479,16 +14479,16 @@
         <v>0</v>
       </c>
       <c r="H227" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="I227" t="n">
         <v>0</v>
       </c>
       <c r="J227" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K227" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="L227" t="n">
         <v>0</v>
@@ -15279,13 +15279,13 @@
         <v>1</v>
       </c>
       <c r="F240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G240" t="n">
         <v>0</v>
       </c>
       <c r="H240" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I240" t="n">
         <v>0</v>
@@ -16454,7 +16454,7 @@
         </is>
       </c>
       <c r="E259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="F259" t="n">
         <v>1</v>
@@ -16469,10 +16469,10 @@
         <v>0</v>
       </c>
       <c r="J259" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K259" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L259" t="n">
         <v>0</v>
@@ -16764,7 +16764,7 @@
         </is>
       </c>
       <c r="E264" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F264" t="n">
         <v>0</v>
@@ -16779,10 +16779,10 @@
         <v>0</v>
       </c>
       <c r="J264" t="n">
+        <v>5</v>
+      </c>
+      <c r="K264" t="n">
         <v>7</v>
-      </c>
-      <c r="K264" t="n">
-        <v>9</v>
       </c>
       <c r="L264" t="n">
         <v>1</v>
@@ -16950,10 +16950,10 @@
         </is>
       </c>
       <c r="E267" t="n">
-        <v>46</v>
+        <v>52</v>
       </c>
       <c r="F267" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="G267" t="n">
         <v>0</v>
@@ -16965,13 +16965,13 @@
         <v>0</v>
       </c>
       <c r="J267" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="K267" t="n">
-        <v>46</v>
+        <v>53</v>
       </c>
       <c r="L267" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M267" t="n">
         <v>0</v>
@@ -17074,7 +17074,7 @@
         </is>
       </c>
       <c r="E269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F269" t="n">
         <v>2</v>
@@ -17089,10 +17089,10 @@
         <v>0</v>
       </c>
       <c r="J269" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K269" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L269" t="n">
         <v>0</v>
@@ -17136,25 +17136,25 @@
         </is>
       </c>
       <c r="E270" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="F270" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="G270" t="n">
         <v>0</v>
       </c>
       <c r="H270" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="I270" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J270" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K270" t="n">
-        <v>97</v>
+        <v>101</v>
       </c>
       <c r="L270" t="n">
         <v>0</v>
@@ -17322,10 +17322,10 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>219</v>
+        <v>220</v>
       </c>
       <c r="F273" t="n">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="G273" t="n">
         <v>0</v>
@@ -17337,10 +17337,10 @@
         <v>0</v>
       </c>
       <c r="J273" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="K273" t="n">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="L273" t="n">
         <v>2</v>
@@ -17632,7 +17632,7 @@
         </is>
       </c>
       <c r="E278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F278" t="n">
         <v>0</v>
@@ -17647,10 +17647,10 @@
         <v>0</v>
       </c>
       <c r="J278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K278" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L278" t="n">
         <v>0</v>
@@ -18004,16 +18004,16 @@
         </is>
       </c>
       <c r="E284" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F284" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="G284" t="n">
         <v>0</v>
       </c>
       <c r="H284" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I284" t="n">
         <v>0</v>
@@ -18022,7 +18022,7 @@
         <v>0</v>
       </c>
       <c r="K284" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="L284" t="n">
         <v>0</v>
@@ -20732,10 +20732,10 @@
         </is>
       </c>
       <c r="E328" t="n">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F328" t="n">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="G328" t="n">
         <v>0</v>
@@ -20747,10 +20747,10 @@
         <v>0</v>
       </c>
       <c r="J328" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="K328" t="n">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="L328" t="n">
         <v>2</v>
@@ -20980,28 +20980,28 @@
         </is>
       </c>
       <c r="E332" t="n">
-        <v>973</v>
+        <v>971</v>
       </c>
       <c r="F332" t="n">
-        <v>814</v>
+        <v>840</v>
       </c>
       <c r="G332" t="n">
         <v>0</v>
       </c>
       <c r="H332" t="n">
-        <v>156</v>
+        <v>126</v>
       </c>
       <c r="I332" t="n">
         <v>0</v>
       </c>
       <c r="J332" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K332" t="n">
-        <v>979</v>
+        <v>978</v>
       </c>
       <c r="L332" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M332" t="n">
         <v>0</v>
@@ -21042,7 +21042,7 @@
         </is>
       </c>
       <c r="E333" t="n">
-        <v>638</v>
+        <v>637</v>
       </c>
       <c r="F333" t="n">
         <v>515</v>
@@ -21057,13 +21057,13 @@
         <v>0</v>
       </c>
       <c r="J333" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K333" t="n">
         <v>638</v>
       </c>
       <c r="L333" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M333" t="n">
         <v>1</v>
@@ -21166,10 +21166,10 @@
         </is>
       </c>
       <c r="E335" t="n">
+        <v>14</v>
+      </c>
+      <c r="F335" t="n">
         <v>13</v>
-      </c>
-      <c r="F335" t="n">
-        <v>11</v>
       </c>
       <c r="G335" t="n">
         <v>0</v>
@@ -21181,10 +21181,10 @@
         <v>0</v>
       </c>
       <c r="J335" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K335" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="L335" t="n">
         <v>0</v>
@@ -21228,10 +21228,10 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>313</v>
+        <v>309</v>
       </c>
       <c r="F336" t="n">
-        <v>286</v>
+        <v>281</v>
       </c>
       <c r="G336" t="n">
         <v>0</v>
@@ -21243,10 +21243,10 @@
         <v>0</v>
       </c>
       <c r="J336" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K336" t="n">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="L336" t="n">
         <v>2</v>
@@ -21662,7 +21662,7 @@
         </is>
       </c>
       <c r="E343" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F343" t="n">
         <v>1</v>
@@ -21677,10 +21677,10 @@
         <v>0</v>
       </c>
       <c r="J343" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K343" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L343" t="n">
         <v>1</v>
@@ -21786,10 +21786,10 @@
         </is>
       </c>
       <c r="E345" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="F345" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="G345" t="n">
         <v>0</v>
@@ -21804,7 +21804,7 @@
         <v>0</v>
       </c>
       <c r="K345" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="L345" t="n">
         <v>0</v>
@@ -22037,7 +22037,7 @@
         <v>16</v>
       </c>
       <c r="F349" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G349" t="n">
         <v>0</v>
@@ -22049,7 +22049,7 @@
         <v>0</v>
       </c>
       <c r="J349" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K349" t="n">
         <v>16</v>
@@ -22158,7 +22158,7 @@
         </is>
       </c>
       <c r="E351" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F351" t="n">
         <v>2</v>
@@ -22173,10 +22173,10 @@
         <v>0</v>
       </c>
       <c r="J351" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K351" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L351" t="n">
         <v>0</v>
@@ -22344,7 +22344,7 @@
         </is>
       </c>
       <c r="E354" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F354" t="n">
         <v>3</v>
@@ -22359,10 +22359,10 @@
         <v>0</v>
       </c>
       <c r="J354" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K354" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L354" t="n">
         <v>0</v>
@@ -22778,10 +22778,10 @@
         </is>
       </c>
       <c r="E361" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="F361" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="G361" t="n">
         <v>0</v>
@@ -22793,10 +22793,10 @@
         <v>0</v>
       </c>
       <c r="J361" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K361" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="L361" t="n">
         <v>0</v>
@@ -22840,7 +22840,7 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F362" t="n">
         <v>0</v>
@@ -22855,10 +22855,10 @@
         <v>0</v>
       </c>
       <c r="J362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K362" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L362" t="n">
         <v>0</v>
@@ -24080,10 +24080,10 @@
         </is>
       </c>
       <c r="E382" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="F382" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G382" t="n">
         <v>0</v>
@@ -24098,7 +24098,7 @@
         <v>0</v>
       </c>
       <c r="K382" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="L382" t="n">
         <v>0</v>
@@ -24204,10 +24204,10 @@
         </is>
       </c>
       <c r="E384" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F384" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="G384" t="n">
         <v>0</v>
@@ -24219,10 +24219,10 @@
         <v>0</v>
       </c>
       <c r="J384" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K384" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L384" t="n">
         <v>0</v>
@@ -24328,7 +24328,7 @@
         </is>
       </c>
       <c r="E386" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F386" t="n">
         <v>5</v>
@@ -24337,7 +24337,7 @@
         <v>0</v>
       </c>
       <c r="H386" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I386" t="n">
         <v>0</v>
@@ -24346,7 +24346,7 @@
         <v>0</v>
       </c>
       <c r="K386" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="L386" t="n">
         <v>0</v>
@@ -24576,7 +24576,7 @@
         </is>
       </c>
       <c r="E390" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F390" t="n">
         <v>4</v>
@@ -24585,7 +24585,7 @@
         <v>0</v>
       </c>
       <c r="H390" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="I390" t="n">
         <v>0</v>
@@ -24594,7 +24594,7 @@
         <v>0</v>
       </c>
       <c r="K390" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="L390" t="n">
         <v>0</v>
@@ -24638,10 +24638,10 @@
         </is>
       </c>
       <c r="E391" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F391" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="G391" t="n">
         <v>0</v>
@@ -24656,7 +24656,7 @@
         <v>0</v>
       </c>
       <c r="K391" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="L391" t="n">
         <v>0</v>
@@ -24703,7 +24703,7 @@
         <v>2</v>
       </c>
       <c r="F392" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="G392" t="n">
         <v>0</v>
@@ -24715,7 +24715,7 @@
         <v>0</v>
       </c>
       <c r="J392" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K392" t="n">
         <v>2</v>
@@ -25754,7 +25754,7 @@
         </is>
       </c>
       <c r="E409" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F409" t="n">
         <v>0</v>
@@ -25769,10 +25769,10 @@
         <v>0</v>
       </c>
       <c r="J409" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="K409" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L409" t="n">
         <v>0</v>
@@ -26002,10 +26002,10 @@
         </is>
       </c>
       <c r="E413" t="n">
+        <v>2</v>
+      </c>
+      <c r="F413" t="n">
         <v>1</v>
-      </c>
-      <c r="F413" t="n">
-        <v>0</v>
       </c>
       <c r="G413" t="n">
         <v>0</v>
@@ -26020,7 +26020,7 @@
         <v>1</v>
       </c>
       <c r="K413" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L413" t="n">
         <v>0</v>
@@ -26067,7 +26067,7 @@
         <v>25</v>
       </c>
       <c r="F414" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="G414" t="n">
         <v>0</v>
@@ -26079,7 +26079,7 @@
         <v>0</v>
       </c>
       <c r="J414" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K414" t="n">
         <v>25</v>
@@ -27056,7 +27056,7 @@
         </is>
       </c>
       <c r="E430" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F430" t="n">
         <v>7</v>
@@ -27065,7 +27065,7 @@
         <v>0</v>
       </c>
       <c r="H430" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I430" t="n">
         <v>0</v>
@@ -27074,7 +27074,7 @@
         <v>0</v>
       </c>
       <c r="K430" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="L430" t="n">
         <v>0</v>
@@ -27121,7 +27121,7 @@
         <v>8</v>
       </c>
       <c r="F431" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="G431" t="n">
         <v>0</v>
@@ -27133,7 +27133,7 @@
         <v>0</v>
       </c>
       <c r="J431" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K431" t="n">
         <v>8</v>
@@ -27428,10 +27428,10 @@
         </is>
       </c>
       <c r="E436" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="F436" t="n">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="G436" t="n">
         <v>0</v>
@@ -27446,7 +27446,7 @@
         <v>2</v>
       </c>
       <c r="K436" t="n">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="L436" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>15</v>
       </c>
       <c r="F442" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="G442" t="n">
         <v>0</v>
@@ -27815,7 +27815,7 @@
         <v>0</v>
       </c>
       <c r="J442" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K442" t="n">
         <v>15</v>
@@ -27865,7 +27865,7 @@
         <v>14</v>
       </c>
       <c r="F443" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="G443" t="n">
         <v>0</v>
@@ -27877,7 +27877,7 @@
         <v>0</v>
       </c>
       <c r="J443" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K443" t="n">
         <v>14</v>
@@ -27986,10 +27986,10 @@
         </is>
       </c>
       <c r="E445" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="F445" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="G445" t="n">
         <v>0</v>
@@ -28004,7 +28004,7 @@
         <v>2</v>
       </c>
       <c r="K445" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="L445" t="n">
         <v>0</v>
@@ -28110,7 +28110,7 @@
         </is>
       </c>
       <c r="E447" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F447" t="n">
         <v>1</v>
@@ -28119,16 +28119,16 @@
         <v>0</v>
       </c>
       <c r="H447" t="n">
+        <v>1</v>
+      </c>
+      <c r="I447" t="n">
+        <v>0</v>
+      </c>
+      <c r="J447" t="n">
+        <v>0</v>
+      </c>
+      <c r="K447" t="n">
         <v>2</v>
-      </c>
-      <c r="I447" t="n">
-        <v>0</v>
-      </c>
-      <c r="J447" t="n">
-        <v>0</v>
-      </c>
-      <c r="K447" t="n">
-        <v>3</v>
       </c>
       <c r="L447" t="n">
         <v>0</v>
@@ -28423,19 +28423,19 @@
         <v>3</v>
       </c>
       <c r="F452" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="G452" t="n">
         <v>0</v>
       </c>
       <c r="H452" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="I452" t="n">
         <v>0</v>
       </c>
       <c r="J452" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K452" t="n">
         <v>3</v>

--- a/data/raw/inventory/Week 34/Fossil/Seller FBA Inventory (SP-API).xlsx
+++ b/data/raw/inventory/Week 34/Fossil/Seller FBA Inventory (SP-API).xlsx
@@ -5049,7 +5049,7 @@
         <v>5</v>
       </c>
       <c r="F75" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="G75" t="n">
         <v>0</v>
@@ -5061,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="J75" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="K75" t="n">
         <v>5</v>
@@ -14408,7 +14408,7 @@
         </is>
       </c>
       <c r="E226" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="F226" t="n">
         <v>742</v>
@@ -14423,10 +14423,10 @@
         <v>0</v>
       </c>
       <c r="J226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K226" t="n">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="L226" t="n">
         <v>0</v>
@@ -16702,7 +16702,7 @@
         </is>
       </c>
       <c r="E263" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F263" t="n">
         <v>0</v>
@@ -16717,10 +16717,10 @@
         <v>0</v>
       </c>
       <c r="J263" t="n">
+        <v>6</v>
+      </c>
+      <c r="K263" t="n">
         <v>7</v>
-      </c>
-      <c r="K263" t="n">
-        <v>8</v>
       </c>
       <c r="L263" t="n">
         <v>0</v>
@@ -17322,7 +17322,7 @@
         </is>
       </c>
       <c r="E273" t="n">
-        <v>220</v>
+        <v>221</v>
       </c>
       <c r="F273" t="n">
         <v>169</v>
@@ -17337,10 +17337,10 @@
         <v>0</v>
       </c>
       <c r="J273" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="K273" t="n">
-        <v>222</v>
+        <v>223</v>
       </c>
       <c r="L273" t="n">
         <v>2</v>
@@ -21045,7 +21045,7 @@
         <v>637</v>
       </c>
       <c r="F333" t="n">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="G333" t="n">
         <v>0</v>
@@ -21057,7 +21057,7 @@
         <v>0</v>
       </c>
       <c r="J333" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K333" t="n">
         <v>638</v>
@@ -21228,10 +21228,10 @@
         </is>
       </c>
       <c r="E336" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="F336" t="n">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G336" t="n">
         <v>0</v>
@@ -21243,10 +21243,10 @@
         <v>0</v>
       </c>
       <c r="J336" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="K336" t="n">
-        <v>311</v>
+        <v>308</v>
       </c>
       <c r="L336" t="n">
         <v>2</v>
@@ -22840,7 +22840,7 @@
         </is>
       </c>
       <c r="E362" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F362" t="n">
         <v>0</v>
@@ -22855,10 +22855,10 @@
         <v>0</v>
       </c>
       <c r="J362" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="K362" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L362" t="n">
         <v>0</v>
@@ -27118,7 +27118,7 @@
         </is>
       </c>
       <c r="E431" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="F431" t="n">
         <v>7</v>
@@ -27133,10 +27133,10 @@
         <v>0</v>
       </c>
       <c r="J431" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K431" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="L431" t="n">
         <v>0</v>
@@ -27803,7 +27803,7 @@
         <v>15</v>
       </c>
       <c r="F442" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G442" t="n">
         <v>0</v>
@@ -27815,7 +27815,7 @@
         <v>0</v>
       </c>
       <c r="J442" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K442" t="n">
         <v>15</v>
@@ -28252,10 +28252,10 @@
         <v>0</v>
       </c>
       <c r="K449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L449" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M449" t="n">
         <v>0</v>
